--- a/astro-site/public/dl/pack-appcc/18-registro-congelacion-anisakis.xlsx
+++ b/astro-site/public/dl/pack-appcc/18-registro-congelacion-anisakis.xlsx
@@ -680,7 +680,7 @@
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>El RD 1420/2006 obliga a informar al consumidor, con un cartel visible o en la carta, de que el pescado servido crudo o poco cocinado ha sido congelado previamente.</t>
+          <t>El art. 8.2 del RD 1021/2022 —el mismo que derogó el RD 1420/2006— obliga a informar al consumidor, con carteles o en la carta-menú, de que el pescado servido crudo o poco cocinado ha sido congelado previamente.</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
     <row r="46" ht="12.2" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>Base legal: Reg. (CE) 853/2004, Anexo III, Secc. VIII, Cap. III, D y RD 1420/2006, de 1 de diciembre. El tratamiento debe alcanzar -20 °C durante al menos 24 horas EN TODAS LAS PARTES de la pieza, o -35 °C durante al menos 15 horas.</t>
+          <t>Base legal: RD 1021/2022, art. 8.1 (que derogó el RD 1420/2006) y Rgto. (CE) 853/2004, Anexo III, Secc. VIII, Cap. III.D. El tratamiento debe alcanzar -20 °C durante al menos 24 horas EN TODAS LAS PARTES de la pieza, o -35 °C durante al menos 15 horas.</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
     <row r="49" ht="12.2" customHeight="1">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>Informa al cliente: el RD 1420/2006 obliga a poner un cartel visible diciendo que el pescado servido crudo o poco cocinado ha sido congelado previamente.</t>
+          <t>Informa al cliente: el art. 8.2 del RD 1021/2022 —el mismo que derogó el RD 1420/2006— obliga a decir, con carteles o en la carta-menú, que el pescado servido crudo o poco cocinado ha sido congelado previamente.</t>
         </is>
       </c>
     </row>
